--- a/utilities/genetic_diversity/genetic_diversity_r/descriptives_formatted.xlsx
+++ b/utilities/genetic_diversity/genetic_diversity_r/descriptives_formatted.xlsx
@@ -1,21 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arimaite/Documents/GitHub/RSV-wastewater-2024-2025/utilities/genetic_diversity/genetic_diversity_r/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352D3C62-6221-7046-9296-0335254ECE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="600" windowWidth="25280" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="22">
+  <si>
+    <t>genome_region</t>
+  </si>
+  <si>
+    <t>subtype</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>Nucleotide_diversity</t>
+  </si>
+  <si>
+    <t>Richness</t>
+  </si>
+  <si>
+    <t>F gene</t>
+  </si>
+  <si>
+    <t>RSV-A</t>
+  </si>
+  <si>
+    <t>0.0015 (7e-04–0.003)</t>
+  </si>
+  <si>
+    <t>13.624 (11.1802–16.5856)</t>
+  </si>
+  <si>
+    <t>RSV-B</t>
+  </si>
+  <si>
+    <t>4e-04 (2e-04–8e-04)</t>
+  </si>
+  <si>
+    <t>11.2782 (9.8551–13.3753)</t>
+  </si>
+  <si>
+    <t>G gene</t>
+  </si>
+  <si>
+    <t>0.0035 (0.0013–0.0076)</t>
+  </si>
+  <si>
+    <t>37.0551 (31.041–45.0715)</t>
+  </si>
+  <si>
+    <t>0.0029 (7e-04–0.0061)</t>
+  </si>
+  <si>
+    <t>31.1355 (25.641–35.7143)</t>
+  </si>
+  <si>
+    <t>Whole genome</t>
+  </si>
+  <si>
+    <t>0.0038 (0.0025–0.0045)</t>
+  </si>
+  <si>
+    <t>20.3541 (18.4329–22.4529)</t>
+  </si>
+  <si>
+    <t>0.0018 (0.0011–0.0024)</t>
+  </si>
+  <si>
+    <t>14.1156 (11.9168–15.1457)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -32,15 +109,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,14 +131,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -63,13 +170,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +222,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +256,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +291,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,220 +467,245 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="24.5" customWidth="1"/>
+    <col min="4" max="4" width="22.5" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>genome_region</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>subtype</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Shannon_entropy</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Nucleotide_diversity</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Richness</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>F gene</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>RSV-A</t>
-        </is>
-      </c>
-      <c r="C2">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
         <v>51</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.0024 (0.0012–0.0046)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.0015 (7e-04–0.003)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>13.624 (11.1802–16.5856)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>F gene</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>RSV-B</t>
-        </is>
-      </c>
-      <c r="C3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
         <v>69</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>8e-04 (4e-04–0.0013)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4e-04 (2e-04–8e-04)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>11.2782 (9.8551–13.3753)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>G gene</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RSV-A</t>
-        </is>
-      </c>
-      <c r="C4">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2">
         <v>76</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.0056 (0.0023–0.0114)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.0035 (0.0013–0.0076)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>37.0551 (31.041–45.0715)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>G gene</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RSV-B</t>
-        </is>
-      </c>
-      <c r="C5">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2">
         <v>73</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.0045 (0.0016–0.0096)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.0029 (7e-04–0.0061)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>31.1355 (25.641–35.7143)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>RSV-A</t>
-        </is>
-      </c>
-      <c r="C6">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2">
         <v>59</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.0057 (0.0039–0.0067)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.0038 (0.0025–0.0045)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>20.3541 (18.4329–22.4529)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Whole genome</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RSV-B</t>
-        </is>
-      </c>
-      <c r="C7">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
         <v>45</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.0027 (0.0017–0.0037)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.0018 (0.0011–0.0024)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>14.1156 (11.9168–15.1457)</t>
-        </is>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
